--- a/data/raw/sales/Week 34/Fossil/Seller Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 34/Fossil/Seller Sales (SP-API).xlsx
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>26679.66</v>
+        <v>21344.07</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
